--- a/Базы данных/БД_2.xlsx
+++ b/Базы данных/БД_2.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="44">
   <si>
     <t>Код пользователя</t>
   </si>
@@ -61,13 +61,103 @@
   </si>
   <si>
     <t>Код учетки</t>
+  </si>
+  <si>
+    <t>Номер дела</t>
+  </si>
+  <si>
+    <t>А1432</t>
+  </si>
+  <si>
+    <t>А1423</t>
+  </si>
+  <si>
+    <t>А1454</t>
+  </si>
+  <si>
+    <t>А1466</t>
+  </si>
+  <si>
+    <t>Сидоров Д.И</t>
+  </si>
+  <si>
+    <t>Название</t>
+  </si>
+  <si>
+    <t>ПИ-121</t>
+  </si>
+  <si>
+    <t>БИ-122</t>
+  </si>
+  <si>
+    <t>Кол-во человек</t>
+  </si>
+  <si>
+    <t>Название группы</t>
+  </si>
+  <si>
+    <t>Артикул</t>
+  </si>
+  <si>
+    <t>Цена</t>
+  </si>
+  <si>
+    <t>Вместимость</t>
+  </si>
+  <si>
+    <t>Основной</t>
+  </si>
+  <si>
+    <t>Резервный</t>
+  </si>
+  <si>
+    <t>А123</t>
+  </si>
+  <si>
+    <t>А125</t>
+  </si>
+  <si>
+    <t>А124</t>
+  </si>
+  <si>
+    <t>А126</t>
+  </si>
+  <si>
+    <t>Сосисочки</t>
+  </si>
+  <si>
+    <t>Сок</t>
+  </si>
+  <si>
+    <t>Картошка</t>
+  </si>
+  <si>
+    <t>Свекла</t>
+  </si>
+  <si>
+    <t>Код склада</t>
+  </si>
+  <si>
+    <t>МНОГИЕ КО МНОГИМ</t>
+  </si>
+  <si>
+    <t>Код записи</t>
+  </si>
+  <si>
+    <t>Количество</t>
+  </si>
+  <si>
+    <t>…</t>
+  </si>
+  <si>
+    <t>n</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -82,6 +172,32 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -105,9 +221,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -388,17 +509,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B4:J13"/>
+  <dimension ref="B4:N54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="2:10" x14ac:dyDescent="0.25">
@@ -422,7 +546,7 @@
       <c r="I4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="2" t="s">
         <v>0</v>
       </c>
     </row>
@@ -518,7 +642,7 @@
       <c r="I10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10" s="2" t="s">
         <v>0</v>
       </c>
     </row>
@@ -594,7 +718,635 @@
         <v>3</v>
       </c>
     </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16">
+        <v>25</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16">
+        <v>35</v>
+      </c>
+      <c r="J16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17">
+        <v>35</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="H17" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17">
+        <v>15</v>
+      </c>
+      <c r="J17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18">
+        <v>21</v>
+      </c>
+      <c r="G18">
+        <v>3</v>
+      </c>
+      <c r="H18" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18">
+        <v>35</v>
+      </c>
+      <c r="J18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19">
+        <v>20</v>
+      </c>
+      <c r="G19">
+        <v>4</v>
+      </c>
+      <c r="H19" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19">
+        <v>35</v>
+      </c>
+      <c r="J19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23">
+        <v>25</v>
+      </c>
+      <c r="E23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24">
+        <v>35</v>
+      </c>
+      <c r="E24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+      <c r="H24" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25">
+        <v>21</v>
+      </c>
+      <c r="E25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26">
+        <v>20</v>
+      </c>
+      <c r="E26" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="B30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B32" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" t="s">
+        <v>20</v>
+      </c>
+      <c r="I32" t="s">
+        <v>27</v>
+      </c>
+      <c r="J32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" t="s">
+        <v>34</v>
+      </c>
+      <c r="D33">
+        <v>500</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33" t="s">
+        <v>28</v>
+      </c>
+      <c r="I33">
+        <v>5000</v>
+      </c>
+      <c r="J33" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" t="s">
+        <v>35</v>
+      </c>
+      <c r="D34">
+        <v>125</v>
+      </c>
+      <c r="G34">
+        <v>2</v>
+      </c>
+      <c r="H34" t="s">
+        <v>29</v>
+      </c>
+      <c r="I34">
+        <v>2500</v>
+      </c>
+      <c r="J34" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" t="s">
+        <v>36</v>
+      </c>
+      <c r="D35">
+        <v>250</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35" t="s">
+        <v>28</v>
+      </c>
+      <c r="I35">
+        <v>5000</v>
+      </c>
+      <c r="J35" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" t="s">
+        <v>37</v>
+      </c>
+      <c r="D36">
+        <v>135</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36" t="s">
+        <v>28</v>
+      </c>
+      <c r="I36">
+        <v>5000</v>
+      </c>
+      <c r="J36" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B39" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" t="s">
+        <v>26</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H39" t="s">
+        <v>20</v>
+      </c>
+      <c r="I39" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>30</v>
+      </c>
+      <c r="C40" t="s">
+        <v>34</v>
+      </c>
+      <c r="D40">
+        <v>500</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+      <c r="H40" t="s">
+        <v>28</v>
+      </c>
+      <c r="I40">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>32</v>
+      </c>
+      <c r="C41" t="s">
+        <v>35</v>
+      </c>
+      <c r="D41">
+        <v>125</v>
+      </c>
+      <c r="E41">
+        <v>2</v>
+      </c>
+      <c r="G41">
+        <v>2</v>
+      </c>
+      <c r="H41" t="s">
+        <v>29</v>
+      </c>
+      <c r="I41">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" t="s">
+        <v>36</v>
+      </c>
+      <c r="D42">
+        <v>250</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>33</v>
+      </c>
+      <c r="C43" t="s">
+        <v>37</v>
+      </c>
+      <c r="D43">
+        <v>135</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" t="s">
+        <v>36</v>
+      </c>
+      <c r="D44">
+        <v>250</v>
+      </c>
+      <c r="E44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B47" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" t="s">
+        <v>20</v>
+      </c>
+      <c r="D47" t="s">
+        <v>26</v>
+      </c>
+      <c r="E47" s="4"/>
+      <c r="G47" t="s">
+        <v>40</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J47" t="s">
+        <v>41</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" t="s">
+        <v>20</v>
+      </c>
+      <c r="N47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>30</v>
+      </c>
+      <c r="C48" t="s">
+        <v>34</v>
+      </c>
+      <c r="D48">
+        <v>500</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+      <c r="H48" t="s">
+        <v>32</v>
+      </c>
+      <c r="I48">
+        <v>2</v>
+      </c>
+      <c r="J48">
+        <v>50</v>
+      </c>
+      <c r="L48">
+        <v>1</v>
+      </c>
+      <c r="M48" t="s">
+        <v>28</v>
+      </c>
+      <c r="N48">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="49" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>32</v>
+      </c>
+      <c r="C49" t="s">
+        <v>35</v>
+      </c>
+      <c r="D49">
+        <v>125</v>
+      </c>
+      <c r="G49">
+        <v>2</v>
+      </c>
+      <c r="H49" t="s">
+        <v>30</v>
+      </c>
+      <c r="I49">
+        <v>1</v>
+      </c>
+      <c r="J49">
+        <v>500</v>
+      </c>
+      <c r="L49">
+        <v>2</v>
+      </c>
+      <c r="M49" t="s">
+        <v>29</v>
+      </c>
+      <c r="N49">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="50" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" t="s">
+        <v>36</v>
+      </c>
+      <c r="D50">
+        <v>250</v>
+      </c>
+      <c r="G50">
+        <v>3</v>
+      </c>
+      <c r="H50" t="s">
+        <v>31</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+      <c r="J50">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="51" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>33</v>
+      </c>
+      <c r="C51" t="s">
+        <v>37</v>
+      </c>
+      <c r="D51">
+        <v>135</v>
+      </c>
+      <c r="G51">
+        <v>4</v>
+      </c>
+      <c r="H51" t="s">
+        <v>33</v>
+      </c>
+      <c r="I51">
+        <v>1</v>
+      </c>
+      <c r="J51">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="52" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" t="s">
+        <v>36</v>
+      </c>
+      <c r="D52">
+        <v>250</v>
+      </c>
+      <c r="G52">
+        <v>5</v>
+      </c>
+      <c r="H52" t="s">
+        <v>31</v>
+      </c>
+      <c r="I52">
+        <v>2</v>
+      </c>
+      <c r="J52">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="53" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="G53" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="54" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="G54" t="s">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B30:D30"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
